--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134246367</v>
+        <v>134246640</v>
       </c>
       <c r="B3" t="n">
         <v>79978</v>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325037</v>
+        <v>325032</v>
       </c>
       <c r="R3" t="n">
-        <v>6556902</v>
+        <v>6556777</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134246640</v>
+        <v>134246367</v>
       </c>
       <c r="B4" t="n">
         <v>79978</v>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325032</v>
+        <v>325037</v>
       </c>
       <c r="R4" t="n">
-        <v>6556777</v>
+        <v>6556902</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133657352</v>
       </c>
       <c r="B2" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134246640</v>
+        <v>134246367</v>
       </c>
       <c r="B3" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325032</v>
+        <v>325037</v>
       </c>
       <c r="R3" t="n">
-        <v>6556777</v>
+        <v>6556902</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134246367</v>
+        <v>134246640</v>
       </c>
       <c r="B4" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325037</v>
+        <v>325032</v>
       </c>
       <c r="R4" t="n">
-        <v>6556902</v>
+        <v>6556777</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>133657352</v>
       </c>
       <c r="B2" t="n">
-        <v>93264</v>
+        <v>93271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134246367</v>
+        <v>133657353</v>
       </c>
       <c r="B3" t="n">
-        <v>79985</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,14 +815,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Skacktjärnet, ca 125 m NO om nordspetsen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325037</v>
+        <v>324949</v>
       </c>
       <c r="R3" t="n">
-        <v>6556902</v>
+        <v>6556476</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,12 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,25 +867,30 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Tallskog.</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134246640</v>
+        <v>133657355</v>
       </c>
       <c r="B4" t="n">
-        <v>79985</v>
+        <v>93271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -916,14 +921,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mellanfjällen, ca 650 m NV om Mardyveln, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325032</v>
+        <v>325121</v>
       </c>
       <c r="R4" t="n">
-        <v>6556777</v>
+        <v>6556881</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,12 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -968,69 +973,68 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Tallskog.</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134246361</v>
+        <v>134246906</v>
       </c>
       <c r="B5" t="n">
-        <v>5484</v>
+        <v>93271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101920</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Svartetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325037</v>
+        <v>324955</v>
       </c>
       <c r="R5" t="n">
-        <v>6556902</v>
+        <v>6556479</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kläckhål</t>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,39 +1099,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134246677</v>
+        <v>134246367</v>
       </c>
       <c r="B6" t="n">
-        <v>5484</v>
+        <v>79992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1135,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325095</v>
+        <v>325037</v>
       </c>
       <c r="R6" t="n">
-        <v>6556772</v>
+        <v>6556902</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,11 +1173,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ett kläckhål i tallåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,39 +1200,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134246697</v>
+        <v>134246640</v>
       </c>
       <c r="B7" t="n">
-        <v>5484</v>
+        <v>79992</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1243,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>325058</v>
+        <v>325032</v>
       </c>
       <c r="R7" t="n">
-        <v>6556688</v>
+        <v>6556777</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1276,6 @@
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnagspån</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1308,6 +1298,650 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134246890</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svartetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>324955</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6556479</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134246361</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5484</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>101920</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Raggbock</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tragosoma depsarium</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>325037</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6556902</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134246677</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5484</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>101920</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Raggbock</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tragosoma depsarium</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>325095</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6556772</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ett kläckhål i tallåga</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134246697</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5484</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>101920</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Raggbock</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tragosoma depsarium</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>325058</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6556688</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnagspån</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134246438</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>325044</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6556865</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134246734</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>325035</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6556559</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133657352</v>
+        <v>134493953</v>
       </c>
       <c r="B2" t="n">
-        <v>93271</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,40 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mellomtjärnet, ca 60 m NO om nordspetsen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325013</v>
+        <v>324844</v>
       </c>
       <c r="R2" t="n">
-        <v>6556398</v>
+        <v>6556673</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,31 +754,40 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Tallskog.</t>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133657353</v>
+        <v>133657352</v>
       </c>
       <c r="B3" t="n">
         <v>93271</v>
@@ -815,14 +821,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skacktjärnet, ca 125 m NO om nordspetsen, Dls</t>
+          <t>Mellomtjärnet, ca 60 m NO om nordspetsen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>324949</v>
+        <v>325013</v>
       </c>
       <c r="R3" t="n">
-        <v>6556476</v>
+        <v>6556398</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133657355</v>
+        <v>133657353</v>
       </c>
       <c r="B4" t="n">
         <v>93271</v>
@@ -921,14 +927,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 650 m NV om Mardyveln, Dls</t>
+          <t>Skacktjärnet, ca 125 m NO om nordspetsen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325121</v>
+        <v>324949</v>
       </c>
       <c r="R4" t="n">
-        <v>6556881</v>
+        <v>6556476</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,14 +992,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134246906</v>
+        <v>133657355</v>
       </c>
       <c r="B5" t="n">
         <v>93271</v>
@@ -1027,14 +1033,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartetjärnen, Dls</t>
+          <t>Mellanfjällen, ca 650 m NV om Mardyveln, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>324955</v>
+        <v>325121</v>
       </c>
       <c r="R5" t="n">
-        <v>6556479</v>
+        <v>6556881</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,17 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,25 +1085,30 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Tallskog.</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134246367</v>
+        <v>134246906</v>
       </c>
       <c r="B6" t="n">
-        <v>79992</v>
+        <v>93271</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,14 +1139,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Svartetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325037</v>
+        <v>324955</v>
       </c>
       <c r="R6" t="n">
-        <v>6556902</v>
+        <v>6556479</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1211,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134246640</v>
+        <v>134246367</v>
       </c>
       <c r="B7" t="n">
         <v>79992</v>
@@ -1238,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>325032</v>
+        <v>325037</v>
       </c>
       <c r="R7" t="n">
-        <v>6556777</v>
+        <v>6556902</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134246890</v>
+        <v>134246640</v>
       </c>
       <c r="B8" t="n">
         <v>79992</v>
@@ -1335,14 +1346,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartetjärnen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>324955</v>
+        <v>325032</v>
       </c>
       <c r="R8" t="n">
-        <v>6556479</v>
+        <v>6556777</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,54 +1413,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134246361</v>
+        <v>134246890</v>
       </c>
       <c r="B9" t="n">
-        <v>5484</v>
+        <v>79992</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Svartetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>325037</v>
+        <v>324955</v>
       </c>
       <c r="R9" t="n">
-        <v>6556902</v>
+        <v>6556479</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,11 +1487,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,53 +1514,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134246677</v>
+        <v>134493951</v>
       </c>
       <c r="B10" t="n">
-        <v>5484</v>
+        <v>5181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101920</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325095</v>
+        <v>325037</v>
       </c>
       <c r="R10" t="n">
-        <v>6556772</v>
+        <v>6557099</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1584,17 +1584,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ett kläckhål i tallåga</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,26 +1598,40 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134246697</v>
+        <v>134246361</v>
       </c>
       <c r="B11" t="n">
         <v>5484</v>
@@ -1654,7 +1663,11 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1662,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>325058</v>
+        <v>325037</v>
       </c>
       <c r="R11" t="n">
-        <v>6556688</v>
+        <v>6556902</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,7 +1715,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Kläckhål och gnagspån</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,45 +1743,39 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134246438</v>
+        <v>134246677</v>
       </c>
       <c r="B12" t="n">
-        <v>79396</v>
+        <v>5484</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>260591</v>
+        <v>101920</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1776,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>325044</v>
+        <v>325095</v>
       </c>
       <c r="R12" t="n">
-        <v>6556865</v>
+        <v>6556772</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,6 +1819,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett kläckhål i tallåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1839,37 +1851,39 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134246734</v>
+        <v>134246697</v>
       </c>
       <c r="B13" t="n">
-        <v>79396</v>
+        <v>5484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>260591</v>
+        <v>101920</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1877,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>325035</v>
+        <v>325058</v>
       </c>
       <c r="R13" t="n">
-        <v>6556559</v>
+        <v>6556688</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1931,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På tallstam</t>
+          <t>Kläckhål och gnagspån</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,6 +1956,221 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134246438</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>325044</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6556865</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134246734</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>325035</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6556559</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493953</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657352</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657353</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657355</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246906</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246367</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246640</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246890</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1628,6 +1673,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493951</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1740,6 +1790,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246361</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1848,6 +1903,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246677</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246697</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2065,6 +2130,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246438</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2171,8 +2241,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246734</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>